--- a/data/Telegram_Wochenplan_mfx555.xlsx
+++ b/data/Telegram_Wochenplan_mfx555.xlsx
@@ -1,19 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{63612F24-C000-434E-958B-7079A720EF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Wochenplan" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Wochenplan" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Wochenplan!$A$1:$D$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Wochenplan!$A$1:$D$58</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -23,30 +28,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="83">
-  <si>
-    <t xml:space="preserve">Tag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uhrzeit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MONTAG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Morgens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">☀️🚀 Guten Morgen und willkommen in einer neuen Trading-Woche!
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="84">
+  <si>
+    <t>Tag</t>
+  </si>
+  <si>
+    <t>Uhrzeit</t>
+  </si>
+  <si>
+    <t>Slot</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>MONTAG</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>Morgens</t>
+  </si>
+  <si>
+    <t>☀️🚀 Guten Morgen und willkommen in einer neuen Trading-Woche!
 Die Märkte haben übers Wochenende neue Impulse gesammelt, und wir starten heute mit frischen Analysen in @mfx555. Eine neue Woche bedeutet auch: neue Chancen, neue Setups, neue Erkenntnisse.
 Das erwartet euch diese Woche bei uns:
 📊 Tägliche Marktanalysen
@@ -55,13 +60,13 @@
 Lasst uns gemeinsam stark in die Woche starten – schaut vorbei in @mfx555 🔥</t>
   </si>
   <si>
-    <t xml:space="preserve">10:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vormittags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🤖🧠 Wie entstehen eigentlich unsere Analysen?
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>Vormittags</t>
+  </si>
+  <si>
+    <t>🤖🧠 Wie entstehen eigentlich unsere Analysen?
 Viele von euch fragen uns das regelmäßig – zurecht, denn Transparenz ist uns wichtig. Unser AI-Tool wertet in Echtzeit mehrere Datenpunkte gleichzeitig aus:
 📊 Kursbewegungen über verschiedene Zeitebenen
 📶 Handelsvolumen als Bestätigungssignal
@@ -70,13 +75,13 @@
 Neugierig geworden? Mehr dazu in @mfx555 👈</t>
   </si>
   <si>
-    <t xml:space="preserve">12:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mittags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🗓️📈 Wochenausblick: Das steht diese Woche an
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>Mittags</t>
+  </si>
+  <si>
+    <t>🗓️📈 Wochenausblick: Das steht diese Woche an
 Im Laufe der Woche werden mehrere wichtige Wirtschaftsdaten veröffentlicht, die den Forex-Markt spürbar bewegen können – etwa Zinsentscheidungen, Inflationsdaten oder Arbeitsmarktzahlen.
 Warum das wichtig ist:
 ⚡ Hohe Volatilität rund um solche Termine
@@ -85,13 +90,13 @@
 Wir halten euch in @mfx555 zu allen relevanten Terminen auf dem Laufenden, damit ihr nicht überrascht werdet.</t>
   </si>
   <si>
-    <t xml:space="preserve">15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nachmittags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🔍 Was bringt euch eigentlich unsere VIP-Gruppe?
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>Nachmittags</t>
+  </si>
+  <si>
+    <t>🔍 Was bringt euch eigentlich unsere VIP-Gruppe?
 Viele fragen uns, was der Unterschied zur kostenlosen Basis-Gruppe ist. Hier die Übersicht:
 ✅ Tägliche, detaillierte Signale mit Entry/Stop/Target
 🤖 Voller Zugriff auf unser AI-Analyse-Tool
@@ -101,25 +106,25 @@
 Wer dabei sein möchte, meldet sich einfach in @mfx555 👈</t>
   </si>
   <si>
-    <t xml:space="preserve">17:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Später Nachmittag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">💬❤️ Feedback aus unserer Community
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>Später Nachmittag</t>
+  </si>
+  <si>
+    <t>💬❤️ Feedback aus unserer Community
 Uns erreichen regelmäßig Nachrichten von Mitgliedern, die uns zeigen, dass unser Ansatz ankommt:
 „Ich schätze besonders, dass die Analysen nachvollziehbar erklärt werden – das hat mir wirklich geholfen, den Markt besser zu verstehen." – Mitglied der VIP-Gruppe
 Genau das ist unser Anspruch: Transparenz statt leerer Versprechen, Erklärungen statt reiner Signale ohne Kontext 🙌 Wenn ihr das auch erleben möchtet, kommt vorbei in @mfx555</t>
   </si>
   <si>
-    <t xml:space="preserve">19:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">📢 Noch nicht in der VIP-Gruppe dabei?
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>Abends</t>
+  </si>
+  <si>
+    <t>📢 Noch nicht in der VIP-Gruppe dabei?
 Falls ihr noch überlegt: Es gibt keinen Haken. Die VIP-Gruppe ist zu 100% kostenlos 🆓 – ihr bekommt einfach mehr:
 🎯 Mehr Signale
 🤖 Mehr AI-Auswertungen
@@ -127,38 +132,38 @@
 Meldet euch einfach in @mfx555, und wir nehmen euch mit rein 📝</t>
   </si>
   <si>
-    <t xml:space="preserve">21:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Später Abend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">📚 Ohne Plan kein nachhaltiger Erfolg
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>Später Abend</t>
+  </si>
+  <si>
+    <t>📚 Ohne Plan kein nachhaltiger Erfolg
 Fragt euch ehrlich: Wisst ihr vor jedem Trade genau, wo euer Entry, euer Stop, euer Ziel und eure Positionsgröße liegen? Genau darüber sprechen wir regelmäßig in der VIP-Gruppe – nicht nur über die Signale selbst, sondern über die Struktur dahinter 🛡️
 Ein Trading-Plan hilft, Entscheidungen im Moment nicht aus dem Bauch heraus zu treffen, sondern nach klaren Regeln.
 ⚠️ *Hinweis: Trading ist mit Verlustrisiken verbunden – dies ist keine Anlageberatung.*</t>
   </si>
   <si>
-    <t xml:space="preserve">23:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nacht</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🌙 Guter erster Tag der neuen Woche!
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>Nacht</t>
+  </si>
+  <si>
+    <t>🌙 Guter erster Tag der neuen Woche!
 Danke, dass ihr heute in @mfx555 dabei wart – ob als stille Mitleser oder aktive Teilnehmer der Diskussion 🙏 Morgen geht es mit neuen Analysen weiter.
 Kommt gut zur Ruhe, bis morgen früh! 😴✨</t>
   </si>
   <si>
-    <t xml:space="preserve">DIENSTAG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">☕📈 Guten Morgen zusammen!
+    <t>DIENSTAG</t>
+  </si>
+  <si>
+    <t>☕📈 Guten Morgen zusammen!
 Der Wochenstart war stark, und wir setzen den Schwung heute fort. In @mfx555 schauen wir uns gemeinsam die aktuellen Setups im Forex-Markt an und ordnen ein, was gestern und über Nacht passiert ist.
 Startet konzentriert in den Tag – wir begleiten euch dabei 🚀</t>
   </si>
   <si>
-    <t xml:space="preserve">🔎 Feature-Deep-Dive: Trendwechsel frühzeitig erkennen
+    <t>🔎 Feature-Deep-Dive: Trendwechsel frühzeitig erkennen
 Eine der Stärken unseres AI-Tools ist die Mustererkennung über große Datenmengen hinweg. Dadurch kann es Trendwechsel oft früher erkennen, als es mit bloßem Auge möglich wäre 👁️
 Konkret bedeutet das:
 📉 Frühere Warnsignale bei Trendumkehrungen
@@ -167,13 +172,13 @@
 In der kostenlosen VIP-Gruppe bekommt ihr diese Auswertungen live mitgeteilt 📲 Schaut vorbei in @mfx555</t>
   </si>
   <si>
-    <t xml:space="preserve">📊 Kurzes Zwischen-Update
+    <t>📊 Kurzes Zwischen-Update
 [ERGEBNIS] – so haben sich unsere Setups diese Woche bisher entwickelt. Wir zeigen euch das bewusst offen, auch wenn nicht jeder Trade aufgeht 🤷‍♂️ Das gehört zum Trading dazu, und genau deshalb ist Risikomanagement so entscheidend.
 Transparenz ist uns wichtiger als eine geschönte Darstellung.
 ⚠️ *Vergangene Ergebnisse sind keine Garantie für zukünftige Erfolge.*</t>
   </si>
   <si>
-    <t xml:space="preserve">👥 Warum bleibt unsere VIP-Gruppe bewusst überschaubar?
+    <t>👥 Warum bleibt unsere VIP-Gruppe bewusst überschaubar?
 Wir könnten die Gruppe beliebig wachsen lassen, tun das aber bewusst nicht. Der Grund:
 🎯 Qualität der Diskussionen bleibt hoch
 💬 Persönlicher Austausch bleibt möglich
@@ -181,7 +186,7 @@
 Auch wenn die Gruppe kostenlos ist 🆓, legen wir Wert auf diese Struktur. Interesse an einem Platz? Meldet euch in @mfx555 👈</t>
   </si>
   <si>
-    <t xml:space="preserve">💡 Trading-Tipp des Tages
+    <t>💡 Trading-Tipp des Tages
 Geduld schlägt Hektik. Eine der häufigsten Fehlerquellen im Trading ist, ein Setup zu erzwingen, das noch nicht wirklich passt ⏳
 Besser:
 ✅ Warten, bis alle Kriterien erfüllt sind
@@ -190,11 +195,11 @@
 Diese Disziplin unterscheidet oft erfolgreiche von frustrierten Tradern.</t>
   </si>
   <si>
-    <t xml:space="preserve">👋 Noch dabei heute Abend?
+    <t>👋 Noch dabei heute Abend?
 Wer noch in die kostenlose VIP-Gruppe möchte, kann das jederzeit unkompliziert tun – kein Papierkram, keine Kosten 🆓 Einfach @mfx555 kontaktieren und wir kümmern uns um den Rest 📝</t>
   </si>
   <si>
-    <t xml:space="preserve">🧠 Trading-Psychologie: Der eigentliche Gegner
+    <t>🧠 Trading-Psychologie: Der eigentliche Gegner
 Die größten Hürden beim Trading sind selten der Markt selbst, sondern die eigenen Emotionen:
 😨 Angst, eine Chance zu verpassen (FOMO)
 🤑 Gier nach einem größeren Gewinn
@@ -203,18 +208,18 @@
 ⚠️ *Bitte handelt nur mit Kapital, dessen Verlust ihr verkraften könnt.*</t>
   </si>
   <si>
-    <t xml:space="preserve">🌙 Guter Dienstag, alle zusammen!
+    <t>🌙 Guter Dienstag, alle zusammen!
 Danke fürs Mitlesen, Mitdiskutieren und für eure Fragen heute in @mfx555 🙌 Morgen ist bereits Halbzeit der Woche – bis dahin, schlaft gut 😴</t>
   </si>
   <si>
-    <t xml:space="preserve">MITTWOCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">☀️🙌 Guten Morgen, Halbzeit der Woche!
+    <t>MITTWOCH</t>
+  </si>
+  <si>
+    <t>☀️🙌 Guten Morgen, Halbzeit der Woche!
 Zwei Handelstage liegen hinter uns, zwei-drei weitere folgen noch. Ein guter Moment, um kurz durchzuatmen und mit klarem Kopf in den Tag zu starten. Aktuelle Setups und Analysen findet ihr wie gewohnt in @mfx555 📊</t>
   </si>
   <si>
-    <t xml:space="preserve">🤖 Was unser AI-Tool wirklich besonders macht
+    <t>🤖 Was unser AI-Tool wirklich besonders macht
 Anders als reines Bauchgefühl bewertet unser Tool den Markt konsequent datenbasiert – ohne Tagesform, ohne Emotionen 📉📈
 Das bedeutet konkret:
 📊 Gleichbleibende Kriterien bei jeder Analyse
@@ -223,12 +228,12 @@
 Die vollständigen Auswertungen findet ihr kostenlos in unserer VIP-Gruppe 🆓 – schaut vorbei in @mfx555</t>
   </si>
   <si>
-    <t xml:space="preserve">💬 Frage an euch: Was beschäftigt euch diese Woche?
+    <t>💬 Frage an euch: Was beschäftigt euch diese Woche?
 Welches Währungspaar habt ihr aktuell besonders im Blick? EUR/USD, GBP/USD, USD/JPY oder etwas ganz anderes? 👀
 Schreibt es uns einfach in @mfx555 – wir greifen die spannendsten Fragen in unseren nächsten Analysen auf und gehen im Detail darauf ein.</t>
   </si>
   <si>
-    <t xml:space="preserve">🔍 Ein VIP-Vorteil, der oft unterschätzt wird
+    <t>🔍 Ein VIP-Vorteil, der oft unterschätzt wird
 Neben Signalen und AI-Auswertungen gibt es einen Punkt, den viele Mitglieder besonders schätzen: den direkten Austausch mit dem Team 💬
 Egal ob Fragen zu:
 📊 einem konkreten Setup
@@ -237,16 +242,16 @@
 Wir beantworten es persönlich – und das komplett kostenlos 🆓 Mehr dazu in @mfx555</t>
   </si>
   <si>
-    <t xml:space="preserve">💬❤️ Community-Feedback
+    <t>💬❤️ Community-Feedback
 „Ich habe durch die Erklärungen in der VIP-Gruppe endlich richtig verstanden, warum ein Stop-Loss so wichtig ist – nicht nur theoretisch, sondern in der Praxis." – Mitglied der Gruppe
 Solche Nachrichten zeigen uns, dass es nicht nur um Signale geht, sondern um echtes Verständnis. Genau das motiviert uns jeden Tag aufs Neue 🙏</t>
   </si>
   <si>
-    <t xml:space="preserve">📢 Kurzer Reminder zur Wochenmitte
+    <t>📢 Kurzer Reminder zur Wochenmitte
 Die VIP-Gruppe kostet nach wie vor nichts 🆓 – aber sie bringt spürbar mehr Struktur und Tiefe in euer Trading. Falls ihr noch nicht dabei seid: einfach in @mfx555 melden, der Einstieg dauert nur eine Minute 📝</t>
   </si>
   <si>
-    <t xml:space="preserve">🛡️ Risikomanagement-Tipp: Die 1-2%-Regel
+    <t>🛡️ Risikomanagement-Tipp: Die 1-2%-Regel
 Eine einfache, aber wirkungsvolle Faustregel: Riskiert pro Trade nie mehr als 1-2% eures Gesamtkontos 📏
 Warum das funktioniert:
 ✅ Eine Verlustserie bringt euch nicht aus der Bahn
@@ -256,18 +261,18 @@
 ⚠️ *Trading ist mit Verlustrisiken verbunden – dies ist keine Anlageberatung.*</t>
   </si>
   <si>
-    <t xml:space="preserve">🌙 Mittwoch geschafft, Halbzeit erfolgreich hinter uns!
+    <t>🌙 Mittwoch geschafft, Halbzeit erfolgreich hinter uns!
 Danke für eure Fragen, euer Feedback und eure Beteiligung heute in @mfx555 🙌 Morgen geht es weiter Richtung Wochenende – gute Nacht euch allen 😴</t>
   </si>
   <si>
-    <t xml:space="preserve">DONNERSTAG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">☀️📊 Guten Morgen zusammen!
+    <t>DONNERSTAG</t>
+  </si>
+  <si>
+    <t>☀️📊 Guten Morgen zusammen!
 Nur noch zwei Handelstage bis zum Wochenende – genug Zeit, um noch spannende Setups mitzunehmen. Heute werfen wir wieder einen genauen Blick auf den Forex-Markt in @mfx555. Startet fokussiert in den Tag 🚀</t>
   </si>
   <si>
-    <t xml:space="preserve">🤖🔍 So erkennt unser AI-Tool Setups im Detail
+    <t>🤖🔍 So erkennt unser AI-Tool Setups im Detail
 Das Tool arbeitet nicht mit einer einzelnen Kennzahl, sondern kombiniert mehrere Ebenen gleichzeitig:
 ⏱️ Mehrere Zeitebenen parallel (z. B. Tages- und Stundenchart)
 📶 Indikatoren zur Bestätigung von Trends
@@ -275,7 +280,7 @@
 Diese Kombination ermöglicht eine schnellere und fundiertere Einschätzung, als es manuell möglich wäre ⚡ Die vollständige Analyse dazu gibt's kostenlos in der VIP-Gruppe 🆓 @mfx555</t>
   </si>
   <si>
-    <t xml:space="preserve">📊🖼️ Ergebnis-Update mit Chart und Begründung
+    <t>📊🖼️ Ergebnis-Update mit Chart und Begründung
 [ERGEBNIS] – so hat sich die Woche bisher entwickelt. Wie immer zeigen wir das transparent, inklusive der Trades, die nicht aufgegangen sind.
 Warum wir das so handhaben:
 🔎 Nachvollziehbarkeit statt Schönfärberei
@@ -283,7 +288,7 @@
 📚 Auch aus Verlust-Trades lässt sich lernen</t>
   </si>
   <si>
-    <t xml:space="preserve">🗓️ VIP-Vorteil im Fokus: Wöchentliche Marktüberblicke
+    <t>🗓️ VIP-Vorteil im Fokus: Wöchentliche Marktüberblicke
 Neben den täglichen Signalen bekommt ihr in der VIP-Gruppe regelmäßig einen strukturierten Wochenüberblick, der euch hilft, die großen Bewegungen richtig einzuordnen:
 📈 Welche Trends dominieren aktuell?
 📰 Welche Ereignisse haben den Markt bewegt?
@@ -291,7 +296,7 @@
 Und das komplett kostenlos 🆓 Mehr dazu in @mfx555</t>
   </si>
   <si>
-    <t xml:space="preserve">📚 Aus Fehlern lernen: auch Profis machen Verlust-Trades
+    <t>📚 Aus Fehlern lernen: auch Profis machen Verlust-Trades
 Auch erfahrene Trader liegen regelmäßig falsch – der entscheidende Unterschied liegt nicht im "immer richtig liegen", sondern darin:
 🛡️ Wie diszipliniert wird das Risiko begrenzt?
 📏 Wird die Positionsgröße konsequent eingehalten?
@@ -299,11 +304,11 @@
 Genau diese Themen besprechen wir regelmäßig gemeinsam in der VIP-Gruppe.</t>
   </si>
   <si>
-    <t xml:space="preserve">📢 Wer noch überlegt, ob sich der Einstieg lohnt
+    <t>📢 Wer noch überlegt, ob sich der Einstieg lohnt
 Die VIP-Gruppe ist kostenlos, unverbindlich und jederzeit kündbar – es gibt schlicht keinen Nachteil, es einmal auszuprobieren 🆓✨ Meldet euch einfach in @mfx555 und schaut es euch selbst an.</t>
   </si>
   <si>
-    <t xml:space="preserve">💰 Money-Management-Basics
+    <t>💰 Money-Management-Basics
 Ein oft unterschätzter Baustein erfolgreichen Tradings: die richtige Positionsgröße.
 📏 Positionsgröße immer an Kontogröße anpassen
 🛑 Abstand zum Stop-Loss mit einberechnen
@@ -312,18 +317,18 @@
 ⚠️ *Bitte handelt nur mit Kapital, dessen Verlust ihr verkraften könnt.*</t>
   </si>
   <si>
-    <t xml:space="preserve">🌙 Donnerstag erfolgreich im Kasten!
+    <t>🌙 Donnerstag erfolgreich im Kasten!
 Morgen steht der letzte Handelstag der Woche an – wir sind gespannt, was der Markt noch bringt. Danke für eure Beteiligung heute in @mfx555 🙏 Gute Nacht euch allen 😴</t>
   </si>
   <si>
-    <t xml:space="preserve">FREITAG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">☀️🎯 Guten Morgen zum letzten Handelstag der Woche!
+    <t>FREITAG</t>
+  </si>
+  <si>
+    <t>☀️🎯 Guten Morgen zum letzten Handelstag der Woche!
 Lasst uns die Woche stark abschließen. Wie gewohnt findet ihr alle aktuellen Setups und Analysen in @mfx555 📊 Ein guter Start in den Freitag legt oft den Grundstein für einen entspannten Wochenausklang 🚀</t>
   </si>
   <si>
-    <t xml:space="preserve">🤖📅 Wochen-Rückblick unseres AI-Tools
+    <t>🤖📅 Wochen-Rückblick unseres AI-Tools
 Diese Woche hat uns das Tool geholfen, mehrere Trendwechsel frühzeitig zu erkennen – ein gutes Beispiel dafür, wie datenbasierte Analyse in der Praxis funktioniert.
 Was wir diese Woche beobachtet haben:
 📉 Mehrere klare Trendbestätigungen
@@ -332,12 +337,12 @@
 Die vollständige Auswertung gibt's wie immer kostenlos in der VIP-Gruppe 🆓 @mfx555</t>
   </si>
   <si>
-    <t xml:space="preserve">📊🖼️ Wochenrückblick: So lief die Woche insgesamt
+    <t>📊🖼️ Wochenrückblick: So lief die Woche insgesamt
 [ERGEBNIS] – transparent und nachvollziehbar zusammengefasst, inklusive der Setups, die nicht funktioniert haben. Wir glauben, dass genau das den Unterschied macht: nicht nur Erfolge zu zeigen, sondern die ganze Realität des Tradings.
 ⚠️ *Vergangene Ergebnisse sind keine Garantie für zukünftige Erfolge.*</t>
   </si>
   <si>
-    <t xml:space="preserve">🎯 Vor dem Wochenende noch schnell dabei sein?
+    <t>🎯 Vor dem Wochenende noch schnell dabei sein?
 Wer sich jetzt der VIP-Gruppe anschließt, verpasst am Montag keine der ersten Analysen der neuen Woche mehr 🆓
 Vorteile im Überblick:
 🤖 AI-gestützte Setups ab dem ersten Handelstag
@@ -346,15 +351,15 @@
 Einfach in @mfx555 melden – kostenlos und unkompliziert.</t>
   </si>
   <si>
-    <t xml:space="preserve">🙏❤️ Danke an unsere Community
+    <t>🙏❤️ Danke an unsere Community
 Diese Woche gab es wieder zahlreiche gute Fragen, spannende Diskussionen und ehrliches Feedback in @mfx555. Genau das macht diese Gruppe aus – nicht nur Signale, sondern ein echter Austausch untereinander 🤝</t>
   </si>
   <si>
-    <t xml:space="preserve">🌙📉 Der Forex-Markt schließt übers Wochenende
+    <t>🌙📉 Der Forex-Markt schließt übers Wochenende
 Ein guter Moment, um die Handelswoche noch einmal in Ruhe Revue passieren zu lassen: Welche Trades waren gut geplant? Wo gab es Verbesserungspotenzial? Wer das gemeinsam mit uns reflektieren möchte, ist herzlich eingeladen in @mfx555</t>
   </si>
   <si>
-    <t xml:space="preserve">📓 Bildungs-Tipp fürs Wochenende: Das Trading-Tagebuch
+    <t>📓 Bildungs-Tipp fürs Wochenende: Das Trading-Tagebuch
 Eine der wirkungsvollsten Gewohnheiten erfolgreicher Trader ist ein konsequent geführtes Trading-Tagebuch:
 📝 Grund für den Entry festhalten
 🎯 Ziel und Stop-Loss dokumentieren
@@ -362,29 +367,29 @@
 Das bringt langfristig oft mehr als jedes einzelne Setup für sich genommen.</t>
   </si>
   <si>
-    <t xml:space="preserve">🌙🎉 Die Woche ist geschafft!
+    <t>🌙🎉 Die Woche ist geschafft!
 Danke, dass ihr diese Woche mit uns in @mfx555 unterwegs wart – egal ob mit Fragen, Feedback oder einfach als aufmerksamer Mitleser 🙏 Schönes Wochenende euch allen, bis Montag! 😴✨</t>
   </si>
   <si>
-    <t xml:space="preserve">SAMSTAG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">☕🌤️ Guten Morgen und schönes Wochenende!
+    <t>SAMSTAG</t>
+  </si>
+  <si>
+    <t>☕🌤️ Guten Morgen und schönes Wochenende!
 Der Forex-Markt schläft heute – eine gute Gelegenheit, die vergangene Woche in Ruhe nachzubereiten, statt ständig auf Charts zu schauen. Kommt gerne in @mfx555 vorbei, auch am Wochenende ist dort einiges los 📊</t>
   </si>
   <si>
-    <t xml:space="preserve">📚 Wochenend-Lesetipp
+    <t>📚 Wochenend-Lesetipp
 Nehmt euch heute bewusst Zeit für ein Kapitel über Risikomanagement oder Trading-Psychologie 🧠 Kleine Wissens-Investitionen am Wochenende zahlen sich oft erst unter der Woche richtig aus – wenn es schnell gehen muss und Routine gefragt ist.</t>
   </si>
   <si>
-    <t xml:space="preserve">🖼️📈 Rückblick auf die Charts der Woche
+    <t>🖼️📈 Rückblick auf die Charts der Woche
 In @mfx555 könnt ihr in Ruhe nochmal durch die Analysen der letzten Tage scrollen. Fragt euch dabei:
 🔎 Welche Setups haben besonders gut funktioniert?
 🤔 Wo hätte man vorsichtiger sein können?
 📓 Was nehmt ihr für die kommende Woche mit?</t>
   </si>
   <si>
-    <t xml:space="preserve">🆓👀 Ohne Zeitdruck erklärt: Unsere VIP-Gruppe
+    <t>🆓👀 Ohne Zeitdruck erklärt: Unsere VIP-Gruppe
 Am Wochenende ist genug Ruhe, um sich in aller Seelenruhe anzuschauen, was die VIP-Gruppe bietet – ganz ohne Verkaufsdruck, weil sie ohnehin kostenlos ist:
 🎯 Mehr Signale unter der Woche
 🤖 Vollständige AI-Auswertungen
@@ -392,12 +397,12 @@
 Schaut einfach mal vorbei in @mfx555, ganz unverbindlich.</t>
   </si>
   <si>
-    <t xml:space="preserve">💬❤️ Stimme aus der Community
+    <t>💬❤️ Stimme aus der Community
 „Am Wochenende die Woche noch einmal durchzugehen, hilft mir enorm dabei, aus eigenen Fehlern zu lernen, statt sie zu wiederholen." – Mitglied der VIP-Gruppe
 Genau diese Art von Reflexion fördern wir bewusst in der Gruppe 🙌</t>
   </si>
   <si>
-    <t xml:space="preserve">📊🙋‍♂️🙋‍♀️ Kleine Umfrage an euch
+    <t>📊🙋‍♂️🙋‍♀️ Kleine Umfrage an euch
 Was wünscht ihr euch künftig mehr in der Gruppe?
 1️⃣ Mehr Live-Analysen
 2️⃣ Mehr Bildungsinhalte
@@ -405,31 +410,31 @@
 Schreibt uns eure Antwort in @mfx555 – euer Feedback fließt direkt in die Weiterentwicklung der Gruppe ein.</t>
   </si>
   <si>
-    <t xml:space="preserve">🧘 Mindset-Tipp: Erholung gehört zum Trading dazu
+    <t>🧘 Mindset-Tipp: Erholung gehört zum Trading dazu
 Ein entspanntes Wochenende ist kein verlorenes Wochenende – es ist Teil eines gesunden Trading-Rhythmus. Wer ausgeruht und mit klarem Kopf in die neue Woche startet, trifft in der Regel bessere Entscheidungen als jemand, der ständig am Limit arbeitet 🛡️</t>
   </si>
   <si>
-    <t xml:space="preserve">🌙✨ Schönen Samstagabend euch allen!
+    <t>🌙✨ Schönen Samstagabend euch allen!
 Morgen bereiten wir gemeinsam die neue Handelswoche vor. Bis dahin: genießt den Rest des Wochenendes und kommt gut zur Ruhe 😴</t>
   </si>
   <si>
-    <t xml:space="preserve">SONNTAG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">☀️🙏 Guten Morgen und einen entspannten Sonntag!
+    <t>SONNTAG</t>
+  </si>
+  <si>
+    <t>☀️🙏 Guten Morgen und einen entspannten Sonntag!
 Heute lassen wir es bewusst ruhig angehen, bevor morgen früh eine neue Handelswoche beginnt. Trotzdem gibt es in @mfx555 heute schon erste Gedanken zur kommenden Woche 📊</t>
   </si>
   <si>
-    <t xml:space="preserve">🗓️⚡ Blick auf den Wirtschaftskalender der kommenden Woche
+    <t>🗓️⚡ Blick auf den Wirtschaftskalender der kommenden Woche
 Bereits jetzt lohnt sich ein erster Blick darauf, welche Daten kommende Woche veröffentlicht werden und den Forex-Markt bewegen könnten – etwa Zinsentscheidungen oder Konjunkturdaten 🤖
 Unser AI-Tool bereitet sich bereits jetzt im Hintergrund darauf vor. Details und Termine findet ihr in @mfx555</t>
   </si>
   <si>
-    <t xml:space="preserve">🆓✨ Noch nicht in der VIP-Gruppe dabei?
+    <t>🆓✨ Noch nicht in der VIP-Gruppe dabei?
 Der Sonntag ist ein perfekter Zeitpunkt, um vor dem Wochenstart dazuzustoßen – kostenlos, unverbindlich, und ihr verpasst dann keine der ersten Analysen der neuen Woche mehr 🎯 Einfach in @mfx555 melden.</t>
   </si>
   <si>
-    <t xml:space="preserve">📚🗓️ Bildungsinhalt: Wochenplanung im Trading
+    <t>📚🗓️ Bildungsinhalt: Wochenplanung im Trading
 Wer sonntags ein paar Minuten investiert, um die kommende Woche zu planen, handelt unter der Woche oft ruhiger und überlegter:
 🎯 Welche Setups beobachtet ihr bereits?
 📏 Welche Kurslevels sind besonders wichtig?
@@ -437,31 +442,31 @@
 Wer plant, handelt in der Regel entspannter als jemand, der spontan reagiert.</t>
   </si>
   <si>
-    <t xml:space="preserve">🙏❤️ Danke für eine ganze Woche mit euch
+    <t>🙏❤️ Danke für eine ganze Woche mit euch
 Ob Fragen, Diskussionen, Feedback oder einfach aufmerksames Mitlesen – @mfx555 lebt von eurer Beteiligung. Wir schätzen es sehr, dass ihr Teil dieser Community seid 🤝</t>
   </si>
   <si>
-    <t xml:space="preserve">💪🎯 Motivation für die neue Woche
+    <t>💪🎯 Motivation für die neue Woche
 Jede neue Handelswoche ist eine neue Chance, diszipliniert, mit klarem Plan und ohne Hektik zu handeln. Nehmt euch das für die kommenden Tage bewusst vor.
 ⚠️ *Trading ist mit Verlustrisiken verbunden – dies ist keine Anlageberatung.*</t>
   </si>
   <si>
-    <t xml:space="preserve">👀 Ausblick auf morgen
+    <t>👀 Ausblick auf morgen
 Morgen früh starten wir mit frischen Analysen und neuen Setups in @mfx555. Die VIP-Gruppe steht wie immer allen offen, die tiefer einsteigen möchten – komplett kostenlos 🆓 und ohne jede Verpflichtung.</t>
   </si>
   <si>
-    <t xml:space="preserve">🌙🚀 Die Woche ist rum, eine neue steht bevor
+    <t>🌙🚀 Die Woche ist rum, eine neue steht bevor
 Danke, dass ihr Teil von @mfx555 seid – diese Woche und hoffentlich auch in der kommenden. Gute Nacht und bis morgen früh, wenn es wieder losgeht! 😴✨</t>
+  </si>
+  <si>
+    <t>Hallo ihr lieben</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -470,32 +475,15 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -556,14 +544,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -579,186 +567,65 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="20" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF1F4E78"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD0E0E3"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D2E9"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDDEBF7"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE2EFDA"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEAD1DC"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF2CC"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -817,51 +684,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF1F4E78"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -869,12 +748,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -903,7 +782,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -924,7 +803,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -975,7 +854,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -993,29 +872,28 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D57"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D58"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1029,7 +907,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="195.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:4" ht="195.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1043,7 +921,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="237.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:4" ht="237.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1057,7 +935,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:4" ht="210" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -1071,7 +949,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="237.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:4" ht="237.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1085,7 +963,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:4" ht="153.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -1099,7 +977,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:4" ht="153.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -1113,7 +991,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:4" ht="168" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
@@ -1127,7 +1005,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:4" ht="97.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -1141,7 +1019,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:4" ht="97.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>29</v>
       </c>
@@ -1155,7 +1033,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:4" ht="210" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>29</v>
       </c>
@@ -1169,7 +1047,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:4" ht="153.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>29</v>
       </c>
@@ -1183,7 +1061,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:4" ht="181.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>29</v>
       </c>
@@ -1197,7 +1075,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:4" ht="181.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>29</v>
       </c>
@@ -1211,7 +1089,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>29</v>
       </c>
@@ -1225,7 +1103,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:4" ht="210" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>29</v>
       </c>
@@ -1239,7 +1117,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>29</v>
       </c>
@@ -1253,7 +1131,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
@@ -1267,7 +1145,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="195.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:4" ht="195.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>38</v>
       </c>
@@ -1281,7 +1159,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:4" ht="111.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>38</v>
       </c>
@@ -1295,7 +1173,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:4" ht="181.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>38</v>
       </c>
@@ -1309,7 +1187,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:4" ht="111.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>38</v>
       </c>
@@ -1323,505 +1201,513 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:4" ht="111.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>20</v>
+      <c r="B23" s="16">
+        <v>0.72916666666666663</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="223.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>38</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="223.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>38</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C26" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D26" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="181.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="153.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="181.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="181.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="210" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="210" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B33" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C34" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D34" s="9" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="195.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="195.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="111.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="181.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="168" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B41" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C42" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D42" s="11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
         <v>65</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="126" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
         <v>65</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="126" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
         <v>65</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="168" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
         <v>65</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="153.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="97.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
         <v>65</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="153.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
         <v>65</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
         <v>65</v>
       </c>
       <c r="B49" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B50" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="C50" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="D50" s="13" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B50" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C50" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="14" t="s">
         <v>74</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="111.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="14" t="s">
         <v>74</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="14" t="s">
         <v>74</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="181.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="14" t="s">
         <v>74</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="97.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="14" t="s">
         <v>74</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="97.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="14" t="s">
         <v>74</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>74</v>
       </c>
       <c r="B57" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B58" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C57" s="14" t="s">
+      <c r="C58" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D57" s="15" t="s">
+      <c r="D58" s="15" t="s">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D57"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:D58" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>